--- a/data/trans_orig/IP07KS_C08_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C08_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de divertirse con sus amigos/as en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de divertirse con sus amigos/as, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32928</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26267</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39997</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18329</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13615</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22669</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>58,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44043</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>62910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11611</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5710</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17616</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12844</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8504</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17558</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>41,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23445</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31983</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -946,92 +946,92 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2901</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6991</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47528</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79194</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59407</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48838</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69323</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32860</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26986</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38471</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69941</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>94051</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>80308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104993</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29321</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49474</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19542</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14002</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25411</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,44%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>26,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>27938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>58547</t>
+          <t>60323</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>49579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72120</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -1633,69 +1633,69 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2279</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6506</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3586</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3176</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1659</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45596</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34799</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52836</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>53,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>30546</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11117</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51357</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34261</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53473</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>76627</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40512</t>
+          <t>65483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99532</t>
+          <t>87839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16603</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9956</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27591</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40477</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18672</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>60550</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>56810</t>
+          <t>32790</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92187</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>762</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2423,107 +2423,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4837</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4836</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4875</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35476</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29021</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>41608</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>63,55%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>35980</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>29618</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>41273</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,17%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>37565</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28245</t>
+          <t>31139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71909</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63116</t>
+          <t>64013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81191</t>
+          <t>81254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>17752</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22068</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24683</t>
+          <t>23610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25453</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>495</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>173407</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>157428</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>190120</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>117715</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>73170</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>177040</t>
+          <t>123774</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>158353</t>
+          <t>111427</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>195529</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>294755</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>273982</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>317365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>85097</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>69630</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>100837</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>88841</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>66360</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>83959</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>66763</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>133760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>232921</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>7979</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3787,107 +3787,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1589</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
